--- a/artfynd/A 28450-2023 artfynd.xlsx
+++ b/artfynd/A 28450-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY137"/>
+  <dimension ref="A1:AY139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16951,6 +16951,232 @@
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>114705147</v>
+      </c>
+      <c r="B138" t="n">
+        <v>78446</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Storkorpen, Vb</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>768769</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7145589</v>
+      </c>
+      <c r="S138" t="n">
+        <v>20</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>114709503</v>
+      </c>
+      <c r="B139" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Storkorpen, Vb</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>768769</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7145589</v>
+      </c>
+      <c r="S139" t="n">
+        <v>20</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28450-2023 artfynd.xlsx
+++ b/artfynd/A 28450-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
